--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850D74F8-6F62-4837-8966-012864428F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC07422-A8F4-4EE1-BA42-F551C16E39B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="2" r:id="rId1"/>
@@ -3629,14 +3629,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -3993,7 +3986,7 @@
     </row>
     <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
-        <f>IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A2:A65" si="0">IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -4033,7 +4026,7 @@
     </row>
     <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
-        <f>IF(ISBLANK(I3)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -4073,7 +4066,7 @@
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
-        <f>IF(ISBLANK(I4)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -4113,7 +4106,7 @@
     </row>
     <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
-        <f>IF(ISBLANK(I5)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -4153,7 +4146,7 @@
     </row>
     <row r="6" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
-        <f>IF(ISBLANK(I6)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -4193,7 +4186,7 @@
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
-        <f>IF(ISBLANK(I7)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4233,7 +4226,7 @@
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
-        <f>IF(ISBLANK(I8)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -4273,7 +4266,7 @@
     </row>
     <row r="9" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f>IF(ISBLANK(I9)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -4313,7 +4306,7 @@
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f>IF(ISBLANK(I10)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4353,7 +4346,7 @@
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f>IF(ISBLANK(I11)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -4393,7 +4386,7 @@
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f>IF(ISBLANK(I12)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -4433,7 +4426,7 @@
     </row>
     <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
-        <f>IF(ISBLANK(I13)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4473,7 +4466,7 @@
     </row>
     <row r="14" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
-        <f>IF(ISBLANK(I14)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -4513,7 +4506,7 @@
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f>IF(ISBLANK(I15)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -4553,7 +4546,7 @@
     </row>
     <row r="16" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
-        <f>IF(ISBLANK(I16)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4593,7 +4586,7 @@
     </row>
     <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
-        <f>IF(ISBLANK(I17)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -4633,7 +4626,7 @@
     </row>
     <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
-        <f>IF(ISBLANK(I18)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -4673,7 +4666,7 @@
     </row>
     <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
-        <f>IF(ISBLANK(I19)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -4713,7 +4706,7 @@
     </row>
     <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
-        <f>IF(ISBLANK(I20)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -4753,7 +4746,7 @@
     </row>
     <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
-        <f>IF(ISBLANK(I21)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -4793,7 +4786,7 @@
     </row>
     <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
-        <f>IF(ISBLANK(I22)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -4833,7 +4826,7 @@
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
-        <f>IF(ISBLANK(I23)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -4873,7 +4866,7 @@
     </row>
     <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
-        <f>IF(ISBLANK(I24)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -4913,7 +4906,7 @@
     </row>
     <row r="25" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
-        <f>IF(ISBLANK(I25)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -4953,7 +4946,7 @@
     </row>
     <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
-        <f>IF(ISBLANK(I26)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -4993,7 +4986,7 @@
     </row>
     <row r="27" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
-        <f>IF(ISBLANK(I27)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -5033,7 +5026,7 @@
     </row>
     <row r="28" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
-        <f>IF(ISBLANK(I28)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5073,7 +5066,7 @@
     </row>
     <row r="29" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
-        <f>IF(ISBLANK(I29)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -5113,7 +5106,7 @@
     </row>
     <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
-        <f>IF(ISBLANK(I30)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -5153,7 +5146,7 @@
     </row>
     <row r="31" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
-        <f>IF(ISBLANK(I31)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5193,7 +5186,7 @@
     </row>
     <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
-        <f>IF(ISBLANK(I32)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -5233,7 +5226,7 @@
     </row>
     <row r="33" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
-        <f>IF(ISBLANK(I33)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -5273,7 +5266,7 @@
     </row>
     <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
-        <f>IF(ISBLANK(I34)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -5313,7 +5306,7 @@
     </row>
     <row r="35" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
-        <f>IF(ISBLANK(I35)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -5353,7 +5346,7 @@
     </row>
     <row r="36" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
-        <f>IF(ISBLANK(I36)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -5393,7 +5386,7 @@
     </row>
     <row r="37" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
-        <f>IF(ISBLANK(I37)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -5433,7 +5426,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
-        <f>IF(ISBLANK(I38)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -5473,7 +5466,7 @@
     </row>
     <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
-        <f>IF(ISBLANK(I39)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -5513,7 +5506,7 @@
     </row>
     <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="str">
-        <f>IF(ISBLANK(I40)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -5553,7 +5546,7 @@
     </row>
     <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
-        <f>IF(ISBLANK(I41)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -5593,7 +5586,7 @@
     </row>
     <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
-        <f>IF(ISBLANK(I42)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -5633,7 +5626,7 @@
     </row>
     <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
-        <f>IF(ISBLANK(I43)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -5673,7 +5666,7 @@
     </row>
     <row r="44" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="str">
-        <f>IF(ISBLANK(I44)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -5713,7 +5706,7 @@
     </row>
     <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
-        <f>IF(ISBLANK(I45)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -5753,7 +5746,7 @@
     </row>
     <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="str">
-        <f>IF(ISBLANK(I46)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -5793,7 +5786,7 @@
     </row>
     <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
-        <f>IF(ISBLANK(I47)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -5833,7 +5826,7 @@
     </row>
     <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
-        <f>IF(ISBLANK(I48)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -5873,7 +5866,7 @@
     </row>
     <row r="49" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
-        <f>IF(ISBLANK(I49)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -5913,7 +5906,7 @@
     </row>
     <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
-        <f>IF(ISBLANK(I50)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -5953,7 +5946,7 @@
     </row>
     <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
-        <f>IF(ISBLANK(I51)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -5993,7 +5986,7 @@
     </row>
     <row r="52" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
-        <f>IF(ISBLANK(I52)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -6033,7 +6026,7 @@
     </row>
     <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
-        <f>IF(ISBLANK(I53)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -6073,7 +6066,7 @@
     </row>
     <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
-        <f>IF(ISBLANK(I54)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -6113,7 +6106,7 @@
     </row>
     <row r="55" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
-        <f>IF(ISBLANK(I55)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -6153,7 +6146,7 @@
     </row>
     <row r="56" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
-        <f>IF(ISBLANK(I56)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -6193,7 +6186,7 @@
     </row>
     <row r="57" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
-        <f>IF(ISBLANK(I57)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -6233,7 +6226,7 @@
     </row>
     <row r="58" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
-        <f>IF(ISBLANK(I58)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -6273,7 +6266,7 @@
     </row>
     <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
-        <f>IF(ISBLANK(I59)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -6313,7 +6306,7 @@
     </row>
     <row r="60" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
-        <f>IF(ISBLANK(I60)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -6353,7 +6346,7 @@
     </row>
     <row r="61" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
-        <f>IF(ISBLANK(I61)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -6393,7 +6386,7 @@
     </row>
     <row r="62" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
-        <f>IF(ISBLANK(I62)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -6433,7 +6426,7 @@
     </row>
     <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
-        <f>IF(ISBLANK(I63)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -6473,7 +6466,7 @@
     </row>
     <row r="64" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
-        <f>IF(ISBLANK(I64)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -6513,7 +6506,7 @@
     </row>
     <row r="65" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
-        <f>IF(ISBLANK(I65)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -6553,7 +6546,7 @@
     </row>
     <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
-        <f>IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A66:A129" si="1">IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -6593,7 +6586,7 @@
     </row>
     <row r="67" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
-        <f>IF(ISBLANK(I67)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -6633,7 +6626,7 @@
     </row>
     <row r="68" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
-        <f>IF(ISBLANK(I68)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -6673,7 +6666,7 @@
     </row>
     <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
-        <f>IF(ISBLANK(I69)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -6713,7 +6706,7 @@
     </row>
     <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
-        <f>IF(ISBLANK(I70)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -6753,7 +6746,7 @@
     </row>
     <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
-        <f>IF(ISBLANK(I71)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -6793,7 +6786,7 @@
     </row>
     <row r="72" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
-        <f>IF(ISBLANK(I72)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -6833,7 +6826,7 @@
     </row>
     <row r="73" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="str">
-        <f>IF(ISBLANK(I73)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B73" s="2" t="s">
@@ -6873,7 +6866,7 @@
     </row>
     <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
-        <f>IF(ISBLANK(I74)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -6913,7 +6906,7 @@
     </row>
     <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
-        <f>IF(ISBLANK(I75)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -6953,7 +6946,7 @@
     </row>
     <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
-        <f>IF(ISBLANK(I76)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -6993,7 +6986,7 @@
     </row>
     <row r="77" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
-        <f>IF(ISBLANK(I77)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B77" s="2" t="s">
@@ -7033,7 +7026,7 @@
     </row>
     <row r="78" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="str">
-        <f>IF(ISBLANK(I78)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -7073,7 +7066,7 @@
     </row>
     <row r="79" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="str">
-        <f>IF(ISBLANK(I79)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -7113,7 +7106,7 @@
     </row>
     <row r="80" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="str">
-        <f>IF(ISBLANK(I80)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -7153,7 +7146,7 @@
     </row>
     <row r="81" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="str">
-        <f>IF(ISBLANK(I81)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -7193,7 +7186,7 @@
     </row>
     <row r="82" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="str">
-        <f>IF(ISBLANK(I82)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -7233,7 +7226,7 @@
     </row>
     <row r="83" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="str">
-        <f>IF(ISBLANK(I83)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -7273,7 +7266,7 @@
     </row>
     <row r="84" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="str">
-        <f>IF(ISBLANK(I84)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -7313,7 +7306,7 @@
     </row>
     <row r="85" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="str">
-        <f>IF(ISBLANK(I85)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -7353,7 +7346,7 @@
     </row>
     <row r="86" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="str">
-        <f>IF(ISBLANK(I86)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -7393,7 +7386,7 @@
     </row>
     <row r="87" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="str">
-        <f>IF(ISBLANK(I87)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -7433,7 +7426,7 @@
     </row>
     <row r="88" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="str">
-        <f>IF(ISBLANK(I88)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -7473,7 +7466,7 @@
     </row>
     <row r="89" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="str">
-        <f>IF(ISBLANK(I89)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -7513,7 +7506,7 @@
     </row>
     <row r="90" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="str">
-        <f>IF(ISBLANK(I90)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -7553,7 +7546,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="str">
-        <f>IF(ISBLANK(I91)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B91" s="2" t="s">
@@ -7593,7 +7586,7 @@
     </row>
     <row r="92" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="str">
-        <f>IF(ISBLANK(I92)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -7633,7 +7626,7 @@
     </row>
     <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="str">
-        <f>IF(ISBLANK(I93)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -7673,7 +7666,7 @@
     </row>
     <row r="94" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="str">
-        <f>IF(ISBLANK(I94)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -7713,7 +7706,7 @@
     </row>
     <row r="95" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="str">
-        <f>IF(ISBLANK(I95)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -7753,7 +7746,7 @@
     </row>
     <row r="96" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="str">
-        <f>IF(ISBLANK(I96)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -7793,7 +7786,7 @@
     </row>
     <row r="97" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="str">
-        <f>IF(ISBLANK(I97)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -7833,7 +7826,7 @@
     </row>
     <row r="98" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="str">
-        <f>IF(ISBLANK(I98)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -7873,7 +7866,7 @@
     </row>
     <row r="99" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="str">
-        <f>IF(ISBLANK(I99)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -7913,7 +7906,7 @@
     </row>
     <row r="100" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="str">
-        <f>IF(ISBLANK(I100)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -7953,7 +7946,7 @@
     </row>
     <row r="101" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="str">
-        <f>IF(ISBLANK(I101)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -7993,7 +7986,7 @@
     </row>
     <row r="102" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="str">
-        <f>IF(ISBLANK(I102)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -8033,7 +8026,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="str">
-        <f>IF(ISBLANK(I103)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -8073,7 +8066,7 @@
     </row>
     <row r="104" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="str">
-        <f>IF(ISBLANK(I104)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -8113,7 +8106,7 @@
     </row>
     <row r="105" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="str">
-        <f>IF(ISBLANK(I105)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -8153,7 +8146,7 @@
     </row>
     <row r="106" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="str">
-        <f>IF(ISBLANK(I106)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -8193,7 +8186,7 @@
     </row>
     <row r="107" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="str">
-        <f>IF(ISBLANK(I107)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -8233,7 +8226,7 @@
     </row>
     <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="str">
-        <f>IF(ISBLANK(I108)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -8273,7 +8266,7 @@
     </row>
     <row r="109" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="str">
-        <f>IF(ISBLANK(I109)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -8313,7 +8306,7 @@
     </row>
     <row r="110" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="str">
-        <f>IF(ISBLANK(I110)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -8353,7 +8346,7 @@
     </row>
     <row r="111" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="str">
-        <f>IF(ISBLANK(I111)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -8393,7 +8386,7 @@
     </row>
     <row r="112" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="str">
-        <f>IF(ISBLANK(I112)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -8433,7 +8426,7 @@
     </row>
     <row r="113" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="str">
-        <f>IF(ISBLANK(I113)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -8473,7 +8466,7 @@
     </row>
     <row r="114" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="str">
-        <f>IF(ISBLANK(I114)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -8513,7 +8506,7 @@
     </row>
     <row r="115" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="str">
-        <f>IF(ISBLANK(I115)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -8553,7 +8546,7 @@
     </row>
     <row r="116" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="str">
-        <f>IF(ISBLANK(I116)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -8593,7 +8586,7 @@
     </row>
     <row r="117" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="str">
-        <f>IF(ISBLANK(I117)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -8633,7 +8626,7 @@
     </row>
     <row r="118" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="str">
-        <f>IF(ISBLANK(I118)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -8673,7 +8666,7 @@
     </row>
     <row r="119" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="str">
-        <f>IF(ISBLANK(I119)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B119" s="2" t="s">
@@ -8713,7 +8706,7 @@
     </row>
     <row r="120" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="str">
-        <f>IF(ISBLANK(I120)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -8753,7 +8746,7 @@
     </row>
     <row r="121" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="str">
-        <f>IF(ISBLANK(I121)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B121" s="2" t="s">
@@ -8793,7 +8786,7 @@
     </row>
     <row r="122" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="str">
-        <f>IF(ISBLANK(I122)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B122" s="2" t="s">
@@ -8833,7 +8826,7 @@
     </row>
     <row r="123" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="str">
-        <f>IF(ISBLANK(I123)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B123" s="2" t="s">
@@ -8873,7 +8866,7 @@
     </row>
     <row r="124" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="str">
-        <f>IF(ISBLANK(I124)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B124" s="2" t="s">
@@ -8913,7 +8906,7 @@
     </row>
     <row r="125" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="str">
-        <f>IF(ISBLANK(I125)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B125" s="2" t="s">
@@ -8953,7 +8946,7 @@
     </row>
     <row r="126" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="str">
-        <f>IF(ISBLANK(I126)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -8993,7 +8986,7 @@
     </row>
     <row r="127" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="str">
-        <f>IF(ISBLANK(I127)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B127" s="2" t="s">
@@ -9033,7 +9026,7 @@
     </row>
     <row r="128" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="str">
-        <f>IF(ISBLANK(I128)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B128" s="2" t="s">
@@ -9073,7 +9066,7 @@
     </row>
     <row r="129" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="str">
-        <f>IF(ISBLANK(I129)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B129" s="2" t="s">
@@ -9113,7 +9106,7 @@
     </row>
     <row r="130" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="str">
-        <f>IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A130:A193" si="2">IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B130" s="2" t="s">
@@ -9153,7 +9146,7 @@
     </row>
     <row r="131" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="str">
-        <f>IF(ISBLANK(I131)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B131" s="2" t="s">
@@ -9193,7 +9186,7 @@
     </row>
     <row r="132" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="str">
-        <f>IF(ISBLANK(I132)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B132" s="2" t="s">
@@ -9233,7 +9226,7 @@
     </row>
     <row r="133" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="str">
-        <f>IF(ISBLANK(I133)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B133" s="2" t="s">
@@ -9273,7 +9266,7 @@
     </row>
     <row r="134" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="str">
-        <f>IF(ISBLANK(I134)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B134" s="2" t="s">
@@ -9313,7 +9306,7 @@
     </row>
     <row r="135" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="str">
-        <f>IF(ISBLANK(I135)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -9353,7 +9346,7 @@
     </row>
     <row r="136" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="str">
-        <f>IF(ISBLANK(I136)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B136" s="2" t="s">
@@ -9393,7 +9386,7 @@
     </row>
     <row r="137" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="str">
-        <f>IF(ISBLANK(I137)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B137" s="2" t="s">
@@ -9433,7 +9426,7 @@
     </row>
     <row r="138" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="str">
-        <f>IF(ISBLANK(I138)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B138" s="2" t="s">
@@ -9473,7 +9466,7 @@
     </row>
     <row r="139" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="str">
-        <f>IF(ISBLANK(I139)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B139" s="2" t="s">
@@ -9513,7 +9506,7 @@
     </row>
     <row r="140" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="str">
-        <f>IF(ISBLANK(I140)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B140" s="2" t="s">
@@ -9553,7 +9546,7 @@
     </row>
     <row r="141" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="str">
-        <f>IF(ISBLANK(I141)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B141" s="2" t="s">
@@ -9593,7 +9586,7 @@
     </row>
     <row r="142" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="str">
-        <f>IF(ISBLANK(I142)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B142" s="2" t="s">
@@ -9633,7 +9626,7 @@
     </row>
     <row r="143" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="str">
-        <f>IF(ISBLANK(I143)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B143" s="2" t="s">
@@ -9673,7 +9666,7 @@
     </row>
     <row r="144" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="str">
-        <f>IF(ISBLANK(I144)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B144" s="2" t="s">
@@ -9713,7 +9706,7 @@
     </row>
     <row r="145" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="str">
-        <f>IF(ISBLANK(I145)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B145" s="2" t="s">
@@ -9753,7 +9746,7 @@
     </row>
     <row r="146" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="str">
-        <f>IF(ISBLANK(I146)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B146" s="2" t="s">
@@ -9793,7 +9786,7 @@
     </row>
     <row r="147" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="str">
-        <f>IF(ISBLANK(I147)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B147" s="2" t="s">
@@ -9833,7 +9826,7 @@
     </row>
     <row r="148" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="str">
-        <f>IF(ISBLANK(I148)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B148" s="2" t="s">
@@ -9873,7 +9866,7 @@
     </row>
     <row r="149" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="str">
-        <f>IF(ISBLANK(I149)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B149" s="2" t="s">
@@ -9913,7 +9906,7 @@
     </row>
     <row r="150" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="str">
-        <f>IF(ISBLANK(I150)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -9953,7 +9946,7 @@
     </row>
     <row r="151" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="str">
-        <f>IF(ISBLANK(I151)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B151" s="2" t="s">
@@ -9993,7 +9986,7 @@
     </row>
     <row r="152" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="str">
-        <f>IF(ISBLANK(I152)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -10033,7 +10026,7 @@
     </row>
     <row r="153" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="str">
-        <f>IF(ISBLANK(I153)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -10073,7 +10066,7 @@
     </row>
     <row r="154" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="str">
-        <f>IF(ISBLANK(I154)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -10113,7 +10106,7 @@
     </row>
     <row r="155" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="str">
-        <f>IF(ISBLANK(I155)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -10153,7 +10146,7 @@
     </row>
     <row r="156" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="str">
-        <f>IF(ISBLANK(I156)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -10193,7 +10186,7 @@
     </row>
     <row r="157" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="str">
-        <f>IF(ISBLANK(I157)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -10233,7 +10226,7 @@
     </row>
     <row r="158" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="str">
-        <f>IF(ISBLANK(I158)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -10273,7 +10266,7 @@
     </row>
     <row r="159" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="str">
-        <f>IF(ISBLANK(I159)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B159" s="2" t="s">
@@ -10313,7 +10306,7 @@
     </row>
     <row r="160" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="str">
-        <f>IF(ISBLANK(I160)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -10353,7 +10346,7 @@
     </row>
     <row r="161" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="str">
-        <f>IF(ISBLANK(I161)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B161" s="2" t="s">
@@ -10393,7 +10386,7 @@
     </row>
     <row r="162" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="str">
-        <f>IF(ISBLANK(I162)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -10433,7 +10426,7 @@
     </row>
     <row r="163" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="str">
-        <f>IF(ISBLANK(I163)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -10473,7 +10466,7 @@
     </row>
     <row r="164" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="str">
-        <f>IF(ISBLANK(I164)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -10513,7 +10506,7 @@
     </row>
     <row r="165" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="str">
-        <f>IF(ISBLANK(I165)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -10553,7 +10546,7 @@
     </row>
     <row r="166" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="str">
-        <f>IF(ISBLANK(I166)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B166" s="2" t="s">
@@ -10593,7 +10586,7 @@
     </row>
     <row r="167" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="str">
-        <f>IF(ISBLANK(I167)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B167" s="2" t="s">
@@ -10633,7 +10626,7 @@
     </row>
     <row r="168" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="str">
-        <f>IF(ISBLANK(I168)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -10673,7 +10666,7 @@
     </row>
     <row r="169" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="str">
-        <f>IF(ISBLANK(I169)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B169" s="2" t="s">
@@ -10713,7 +10706,7 @@
     </row>
     <row r="170" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="str">
-        <f>IF(ISBLANK(I170)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B170" s="2" t="s">
@@ -10753,7 +10746,7 @@
     </row>
     <row r="171" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="str">
-        <f>IF(ISBLANK(I171)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B171" s="2" t="s">
@@ -10793,7 +10786,7 @@
     </row>
     <row r="172" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="str">
-        <f>IF(ISBLANK(I172)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B172" s="2" t="s">
@@ -10833,7 +10826,7 @@
     </row>
     <row r="173" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="str">
-        <f>IF(ISBLANK(I173)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B173" s="2" t="s">
@@ -10873,7 +10866,7 @@
     </row>
     <row r="174" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="str">
-        <f>IF(ISBLANK(I174)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B174" s="2" t="s">
@@ -10913,7 +10906,7 @@
     </row>
     <row r="175" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="str">
-        <f>IF(ISBLANK(I175)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B175" s="2" t="s">
@@ -10953,7 +10946,7 @@
     </row>
     <row r="176" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="str">
-        <f>IF(ISBLANK(I176)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -10993,7 +10986,7 @@
     </row>
     <row r="177" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="str">
-        <f>IF(ISBLANK(I177)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B177" s="2" t="s">
@@ -11033,7 +11026,7 @@
     </row>
     <row r="178" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="str">
-        <f>IF(ISBLANK(I178)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B178" s="2" t="s">
@@ -11073,7 +11066,7 @@
     </row>
     <row r="179" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="str">
-        <f>IF(ISBLANK(I179)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B179" s="2" t="s">
@@ -11113,7 +11106,7 @@
     </row>
     <row r="180" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="str">
-        <f>IF(ISBLANK(I180)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B180" s="2" t="s">
@@ -11153,7 +11146,7 @@
     </row>
     <row r="181" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="str">
-        <f>IF(ISBLANK(I181)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B181" s="2" t="s">
@@ -11193,7 +11186,7 @@
     </row>
     <row r="182" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="str">
-        <f>IF(ISBLANK(I182)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -11233,7 +11226,7 @@
     </row>
     <row r="183" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="str">
-        <f>IF(ISBLANK(I183)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B183" s="2" t="s">
@@ -11273,7 +11266,7 @@
     </row>
     <row r="184" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="str">
-        <f>IF(ISBLANK(I184)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -11313,7 +11306,7 @@
     </row>
     <row r="185" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="str">
-        <f>IF(ISBLANK(I185)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B185" s="2" t="s">
@@ -11353,7 +11346,7 @@
     </row>
     <row r="186" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="str">
-        <f>IF(ISBLANK(I186)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -11393,7 +11386,7 @@
     </row>
     <row r="187" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="str">
-        <f>IF(ISBLANK(I187)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -11433,7 +11426,7 @@
     </row>
     <row r="188" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="str">
-        <f>IF(ISBLANK(I188)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B188" s="2" t="s">
@@ -11473,7 +11466,7 @@
     </row>
     <row r="189" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="str">
-        <f>IF(ISBLANK(I189)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B189" s="2" t="s">
@@ -11513,7 +11506,7 @@
     </row>
     <row r="190" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="str">
-        <f>IF(ISBLANK(I190)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B190" s="2" t="s">
@@ -11553,7 +11546,7 @@
     </row>
     <row r="191" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="str">
-        <f>IF(ISBLANK(I191)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B191" s="2" t="s">
@@ -11593,7 +11586,7 @@
     </row>
     <row r="192" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="str">
-        <f>IF(ISBLANK(I192)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B192" s="2" t="s">
@@ -11633,7 +11626,7 @@
     </row>
     <row r="193" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="str">
-        <f>IF(ISBLANK(I193)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B193" s="2" t="s">
@@ -11673,7 +11666,7 @@
     </row>
     <row r="194" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="str">
-        <f>IF(ISBLANK(I194)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A194:A245" si="3">IF(ISBLANK(I194)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -11713,7 +11706,7 @@
     </row>
     <row r="195" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="str">
-        <f>IF(ISBLANK(I195)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B195" s="2" t="s">
@@ -11753,7 +11746,7 @@
     </row>
     <row r="196" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="str">
-        <f>IF(ISBLANK(I196)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B196" s="2" t="s">
@@ -11793,7 +11786,7 @@
     </row>
     <row r="197" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="str">
-        <f>IF(ISBLANK(I197)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B197" s="2" t="s">
@@ -11833,7 +11826,7 @@
     </row>
     <row r="198" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="str">
-        <f>IF(ISBLANK(I198)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B198" s="2" t="s">
@@ -11873,7 +11866,7 @@
     </row>
     <row r="199" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="str">
-        <f>IF(ISBLANK(I199)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B199" s="2" t="s">
@@ -11913,7 +11906,7 @@
     </row>
     <row r="200" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="str">
-        <f>IF(ISBLANK(I200)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -11953,7 +11946,7 @@
     </row>
     <row r="201" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="str">
-        <f>IF(ISBLANK(I201)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B201" s="2" t="s">
@@ -11993,7 +11986,7 @@
     </row>
     <row r="202" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="str">
-        <f>IF(ISBLANK(I202)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -12033,7 +12026,7 @@
     </row>
     <row r="203" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="str">
-        <f>IF(ISBLANK(I203)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B203" s="2" t="s">
@@ -12073,7 +12066,7 @@
     </row>
     <row r="204" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="str">
-        <f>IF(ISBLANK(I204)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B204" s="2" t="s">
@@ -12113,7 +12106,7 @@
     </row>
     <row r="205" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="str">
-        <f>IF(ISBLANK(I205)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B205" s="2" t="s">
@@ -12153,7 +12146,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="str">
-        <f>IF(ISBLANK(I206)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B206" s="2" t="s">
@@ -12193,7 +12186,7 @@
     </row>
     <row r="207" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="str">
-        <f>IF(ISBLANK(I207)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B207" s="2" t="s">
@@ -12233,7 +12226,7 @@
     </row>
     <row r="208" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="str">
-        <f>IF(ISBLANK(I208)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B208" s="2" t="s">
@@ -12273,7 +12266,7 @@
     </row>
     <row r="209" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="str">
-        <f>IF(ISBLANK(I209)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B209" s="2" t="s">
@@ -12313,7 +12306,7 @@
     </row>
     <row r="210" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="str">
-        <f>IF(ISBLANK(I210)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B210" s="2" t="s">
@@ -12353,7 +12346,7 @@
     </row>
     <row r="211" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="str">
-        <f>IF(ISBLANK(I211)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B211" s="2" t="s">
@@ -12393,7 +12386,7 @@
     </row>
     <row r="212" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="str">
-        <f>IF(ISBLANK(I212)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B212" s="2" t="s">
@@ -12433,7 +12426,7 @@
     </row>
     <row r="213" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="str">
-        <f>IF(ISBLANK(I213)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B213" s="2" t="s">
@@ -12473,7 +12466,7 @@
     </row>
     <row r="214" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="str">
-        <f>IF(ISBLANK(I214)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B214" s="2" t="s">
@@ -12513,7 +12506,7 @@
     </row>
     <row r="215" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="str">
-        <f>IF(ISBLANK(I215)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B215" s="2" t="s">
@@ -12553,7 +12546,7 @@
     </row>
     <row r="216" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="str">
-        <f>IF(ISBLANK(I216)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B216" s="2" t="s">
@@ -12593,7 +12586,7 @@
     </row>
     <row r="217" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="str">
-        <f>IF(ISBLANK(I217)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B217" s="2" t="s">
@@ -12633,7 +12626,7 @@
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="str">
-        <f>IF(ISBLANK(I218)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B218" s="2" t="s">
@@ -12673,7 +12666,7 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="str">
-        <f>IF(ISBLANK(I219)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B219" s="2" t="s">
@@ -12713,7 +12706,7 @@
     </row>
     <row r="220" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="str">
-        <f>IF(ISBLANK(I220)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B220" s="2" t="s">
@@ -12753,7 +12746,7 @@
     </row>
     <row r="221" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="str">
-        <f>IF(ISBLANK(I221)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B221" s="2" t="s">
@@ -12793,7 +12786,7 @@
     </row>
     <row r="222" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="str">
-        <f>IF(ISBLANK(I222)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B222" s="2" t="s">
@@ -12833,7 +12826,7 @@
     </row>
     <row r="223" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="str">
-        <f>IF(ISBLANK(I223)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B223" s="2" t="s">
@@ -12873,7 +12866,7 @@
     </row>
     <row r="224" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="str">
-        <f>IF(ISBLANK(I224)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -12913,7 +12906,7 @@
     </row>
     <row r="225" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="str">
-        <f>IF(ISBLANK(I225)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B225" s="2" t="s">
@@ -12953,7 +12946,7 @@
     </row>
     <row r="226" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="str">
-        <f>IF(ISBLANK(I226)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -12993,7 +12986,7 @@
     </row>
     <row r="227" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="str">
-        <f>IF(ISBLANK(I227)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B227" s="2" t="s">
@@ -13033,7 +13026,7 @@
     </row>
     <row r="228" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="str">
-        <f>IF(ISBLANK(I228)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B228" s="2" t="s">
@@ -13073,7 +13066,7 @@
     </row>
     <row r="229" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="str">
-        <f>IF(ISBLANK(I229)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B229" s="2" t="s">
@@ -13113,7 +13106,7 @@
     </row>
     <row r="230" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="str">
-        <f>IF(ISBLANK(I230)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B230" s="2" t="s">
@@ -13153,7 +13146,7 @@
     </row>
     <row r="231" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="str">
-        <f>IF(ISBLANK(I231)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B231" s="2" t="s">
@@ -13193,7 +13186,7 @@
     </row>
     <row r="232" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="str">
-        <f>IF(ISBLANK(I232)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B232" s="2" t="s">
@@ -13233,7 +13226,7 @@
     </row>
     <row r="233" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="str">
-        <f>IF(ISBLANK(I233)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B233" s="2" t="s">
@@ -13273,7 +13266,7 @@
     </row>
     <row r="234" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="str">
-        <f>IF(ISBLANK(I234)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B234" s="2" t="s">
@@ -13313,7 +13306,7 @@
     </row>
     <row r="235" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="str">
-        <f>IF(ISBLANK(I235)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B235" s="2" t="s">
@@ -13353,7 +13346,7 @@
     </row>
     <row r="236" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="str">
-        <f>IF(ISBLANK(I236)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B236" s="2" t="s">
@@ -13393,7 +13386,7 @@
     </row>
     <row r="237" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="str">
-        <f>IF(ISBLANK(I237)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B237" s="2" t="s">
@@ -13433,7 +13426,7 @@
     </row>
     <row r="238" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="str">
-        <f>IF(ISBLANK(I238)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B238" s="2" t="s">
@@ -13473,7 +13466,7 @@
     </row>
     <row r="239" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="str">
-        <f>IF(ISBLANK(I239)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B239" s="2" t="s">
@@ -13513,7 +13506,7 @@
     </row>
     <row r="240" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="str">
-        <f>IF(ISBLANK(I240)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B240" s="2" t="s">
@@ -13553,7 +13546,7 @@
     </row>
     <row r="241" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="str">
-        <f>IF(ISBLANK(I241)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B241" s="2" t="s">
@@ -13593,7 +13586,7 @@
     </row>
     <row r="242" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="str">
-        <f>IF(ISBLANK(I242)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B242" s="2" t="s">
@@ -13633,7 +13626,7 @@
     </row>
     <row r="243" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="str">
-        <f>IF(ISBLANK(I243)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B243" s="2" t="s">
@@ -13673,7 +13666,7 @@
     </row>
     <row r="244" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="str">
-        <f>IF(ISBLANK(I244)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B244" s="2" t="s">
@@ -13713,7 +13706,7 @@
     </row>
     <row r="245" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="str">
-        <f>IF(ISBLANK(I245)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B245" s="2" t="s">
@@ -13756,13 +13749,13 @@
     <sortCondition descending="1" ref="I1:I205"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M1:T215">
-    <cfRule type="expression" dxfId="1" priority="11">
+  <conditionalFormatting sqref="A1:L245">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:L245">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="M1:T215">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
